--- a/project/outputs_xlsx_solution/test_new4.4-wide-NB-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new4.4-wide-NB-1.xlsx
@@ -648,6 +648,18 @@
       <c r="AU1">
         <v>44</v>
       </c>
+      <c r="AV1">
+        <v>45</v>
+      </c>
+      <c r="AW1">
+        <v>46</v>
+      </c>
+      <c r="AX1">
+        <v>47</v>
+      </c>
+      <c r="AY1">
+        <v>48</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -894,6 +906,18 @@
         <v>24</v>
       </c>
       <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1162,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P16" t="s">
         <v>15</v>
@@ -1195,6 +1219,15 @@
         <v>14</v>
       </c>
       <c r="Z16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC16" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1220,22 +1253,16 @@
       <c r="P17" t="s">
         <v>21</v>
       </c>
-      <c r="Z17" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>14</v>
-      </c>
       <c r="AC17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1256,15 +1283,12 @@
         <v>9</v>
       </c>
       <c r="P18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="s">
-        <v>14</v>
-      </c>
-      <c r="R18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1287,13 +1311,13 @@
       <c r="P19" t="s">
         <v>21</v>
       </c>
+      <c r="Q19" t="s">
+        <v>14</v>
+      </c>
       <c r="R19" t="s">
-        <v>14</v>
-      </c>
-      <c r="S19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1314,21 +1338,18 @@
         <v>9</v>
       </c>
       <c r="P20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R20" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="S20" t="s">
-        <v>24</v>
-      </c>
-      <c r="T20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1351,13 +1372,13 @@
       <c r="Q21" t="s">
         <v>21</v>
       </c>
+      <c r="S21" t="s">
+        <v>14</v>
+      </c>
       <c r="T21" t="s">
-        <v>14</v>
-      </c>
-      <c r="U21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1380,13 +1401,13 @@
       <c r="Q22" t="s">
         <v>21</v>
       </c>
+      <c r="T22" t="s">
+        <v>14</v>
+      </c>
       <c r="U22" t="s">
-        <v>14</v>
-      </c>
-      <c r="V22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1422,7 +1443,7 @@
         <v>25</v>
       </c>
       <c r="V23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W23" t="s">
         <v>15</v>
@@ -1434,24 +1455,36 @@
         <v>15</v>
       </c>
       <c r="Z23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC23" t="s">
         <v>14</v>
       </c>
       <c r="AD23" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AF23" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1474,22 +1507,16 @@
       <c r="V24" t="s">
         <v>21</v>
       </c>
-      <c r="AF24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>24</v>
-      </c>
       <c r="AJ24" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AK24" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1510,15 +1537,12 @@
         <v>9</v>
       </c>
       <c r="V25" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1548,15 +1572,12 @@
         <v>26</v>
       </c>
       <c r="Y26" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1577,18 +1598,15 @@
         <v>9</v>
       </c>
       <c r="Y27" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z27" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AA27" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM27" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1611,13 +1629,13 @@
       <c r="Y28" t="s">
         <v>21</v>
       </c>
+      <c r="AA28" t="s">
+        <v>14</v>
+      </c>
       <c r="AB28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AL28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1640,13 +1658,13 @@
       <c r="Y29" t="s">
         <v>21</v>
       </c>
+      <c r="AB29" t="s">
+        <v>14</v>
+      </c>
       <c r="AC29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AL29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN29" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1667,13 +1685,13 @@
         <v>9</v>
       </c>
       <c r="Z30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AB30" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AC30" t="s">
         <v>15</v>
@@ -1685,24 +1703,39 @@
         <v>15</v>
       </c>
       <c r="AF30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO30" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>24</v>
+      </c>
+      <c r="AQ30" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1722,22 +1755,19 @@
       <c r="R31" t="s">
         <v>9</v>
       </c>
-      <c r="Z31" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>24</v>
-      </c>
-      <c r="AP31" t="s">
+      <c r="AC31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT31" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1757,22 +1787,13 @@
       <c r="R32" t="s">
         <v>9</v>
       </c>
-      <c r="Z32" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>24</v>
-      </c>
       <c r="AC32" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AD32" t="s">
         <v>19</v>
       </c>
-      <c r="AP32" t="s">
+      <c r="AT32" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1792,15 +1813,6 @@
       <c r="R33" t="s">
         <v>9</v>
       </c>
-      <c r="Z33" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>26</v>
-      </c>
       <c r="AC33" t="s">
         <v>26</v>
       </c>
@@ -1808,7 +1820,7 @@
         <v>26</v>
       </c>
       <c r="AE33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AF33" t="s">
         <v>14</v>
@@ -1816,7 +1828,7 @@
       <c r="AG33" t="s">
         <v>19</v>
       </c>
-      <c r="AP33" t="s">
+      <c r="AT33" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1836,9 +1848,6 @@
       <c r="S34" t="s">
         <v>9</v>
       </c>
-      <c r="AE34" t="s">
-        <v>21</v>
-      </c>
       <c r="AF34" t="s">
         <v>14</v>
       </c>
@@ -1848,7 +1857,7 @@
       <c r="AH34" t="s">
         <v>19</v>
       </c>
-      <c r="AP34" t="s">
+      <c r="AT34" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1868,7 +1877,7 @@
       <c r="S35" t="s">
         <v>9</v>
       </c>
-      <c r="AE35" t="s">
+      <c r="AF35" t="s">
         <v>21</v>
       </c>
       <c r="AH35" t="s">
@@ -1877,7 +1886,7 @@
       <c r="AI35" t="s">
         <v>19</v>
       </c>
-      <c r="AQ35" t="s">
+      <c r="AU35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1897,7 +1906,7 @@
       <c r="S36" t="s">
         <v>9</v>
       </c>
-      <c r="AE36" t="s">
+      <c r="AF36" t="s">
         <v>21</v>
       </c>
       <c r="AI36" t="s">
@@ -1906,7 +1915,7 @@
       <c r="AJ36" t="s">
         <v>19</v>
       </c>
-      <c r="AQ36" t="s">
+      <c r="AU36" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1926,17 +1935,14 @@
       <c r="T37" t="s">
         <v>9</v>
       </c>
-      <c r="AF37" t="s">
-        <v>21</v>
-      </c>
       <c r="AG37" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AH37" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AI37" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AJ37" t="s">
         <v>15</v>
@@ -1945,21 +1951,33 @@
         <v>15</v>
       </c>
       <c r="AL37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP37" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AQ37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU37" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1979,19 +1997,19 @@
       <c r="V38" t="s">
         <v>9</v>
       </c>
-      <c r="AF38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT38" t="s">
+      <c r="AJ38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AU38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2011,22 +2029,13 @@
       <c r="Y39" t="s">
         <v>9</v>
       </c>
-      <c r="AF39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>24</v>
-      </c>
       <c r="AJ39" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX39" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2046,31 +2055,22 @@
       <c r="Y40" t="s">
         <v>9</v>
       </c>
-      <c r="AF40" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>26</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>26</v>
-      </c>
       <c r="AJ40" t="s">
         <v>26</v>
       </c>
       <c r="AK40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AL40" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AM40" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT40" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX40" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2090,19 +2090,16 @@
       <c r="Y41" t="s">
         <v>9</v>
       </c>
-      <c r="AK41" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>14</v>
-      </c>
       <c r="AM41" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AN41" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT41" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>19</v>
+      </c>
+      <c r="AX41" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2122,16 +2119,16 @@
       <c r="Y42" t="s">
         <v>9</v>
       </c>
-      <c r="AK42" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN42" t="s">
-        <v>14</v>
+      <c r="AM42" t="s">
+        <v>21</v>
       </c>
       <c r="AO42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AU42" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY42" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2151,16 +2148,16 @@
       <c r="Z43" t="s">
         <v>9</v>
       </c>
-      <c r="AK43" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO43" t="s">
-        <v>14</v>
+      <c r="AM43" t="s">
+        <v>21</v>
       </c>
       <c r="AP43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AU43" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY43" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2174,19 +2171,19 @@
       <c r="C44" t="s">
         <v>27</v>
       </c>
-      <c r="AP44" t="s">
-        <v>5</v>
-      </c>
       <c r="AQ44" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AR44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AT44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AU44" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS44" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY44" t="s">
         <v>20</v>
       </c>
     </row>
